--- a/features/driver_distraction/workbook/driver_distraction_00.xlsx
+++ b/features/driver_distraction/workbook/driver_distraction_00.xlsx
@@ -7889,22 +7889,86 @@
         <v>1</v>
       </c>
       <c r="C10" s="82"/>
-      <c r="D10" s="81"/>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-001</t>
+        </is>
+      </c>
       <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="81"/>
+      <c r="F10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-001</t>
+        </is>
+      </c>
+      <c r="G10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Body Off Init</t>
+        </is>
+      </c>
+      <c r="I10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When the vehicle exits Body OFF sleep, DD Service provides Lock Out State initialization and state notification capabilities
+Case [Normal]normal wake-up from Body OFF
+Then DD Service sets all Lock Out States to NOT_RESTRICTED
+(a normal wake-up from Body OFF leaves the locked-out features reachable)</t>
+        </is>
+      </c>
+      <c r="J10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Bring the HU through the Body OFF power down [ASSUMPTION A-DD10]
+2. Start CAN activity on Body CAN to wake the HU [ASSUMPTION A-DD10]
+3. Open "Player Song, artist, title, etc. (speller search)" and check that it opens</t>
+        </is>
+      </c>
+      <c r="M10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The HU periodic messages are no longer present on the bus
+2. The HU broadcasts all its periodic messages within 400 msec of wakeup
+3. "Player Song, artist, title, etc. (speller search)" opens and its view is displayed</t>
+        </is>
+      </c>
+      <c r="N10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915104</t>
+        </is>
+      </c>
+      <c r="O10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
+      <c r="R10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S10" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T10" s="81"/>
       <c r="U10" s="81"/>
       <c r="V10" s="81"/>
@@ -7912,7 +7976,11 @@
       <c r="X10" s="83"/>
       <c r="Y10" s="81"/>
       <c r="Z10" s="83"/>
-      <c r="AA10" s="83"/>
+      <c r="AA10" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB10" s="81"/>
       <c r="AC10" s="81"/>
       <c r="AD10" s="81"/>
@@ -7928,22 +7996,88 @@
         <v/>
       </c>
       <c r="C11" s="82"/>
-      <c r="D11" s="81"/>
+      <c r="D11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-002</t>
+        </is>
+      </c>
       <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="81"/>
+      <c r="F11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-002</t>
+        </is>
+      </c>
+      <c r="G11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Body Off Init</t>
+        </is>
+      </c>
+      <c r="I11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When the DD process is terminated during Body OFF sleep, DD Service provides cold-start state initialization capability after wake-up
+Case [Exception]the process is terminated during sleep
+Then DD Service starts with the default NOT_RESTRICTED state and initializes all states to NOT_RESTRICTED
+(a cold start after the process was terminated during sleep leaves the locked-out features reachable)</t>
+        </is>
+      </c>
+      <c r="J11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Bring the HU through the Body OFF power down [ASSUMPTION A-DD10]
+2. Terminate the DD process in the test environment
+3. Start CAN activity on Body CAN to wake the HU [ASSUMPTION A-DD10]
+4. Open "DND Customize auto reply message" and check that it opens</t>
+        </is>
+      </c>
+      <c r="M11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The HU periodic messages are no longer present on the bus
+2. The DD process is no longer running in the test environment
+3. The HU broadcasts all its periodic messages within 400 msec of wakeup
+4. "DND Customize auto reply message" opens and its view is displayed</t>
+        </is>
+      </c>
+      <c r="N11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915104</t>
+        </is>
+      </c>
+      <c r="O11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
+      <c r="R11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S11" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T11" s="81"/>
       <c r="U11" s="81"/>
       <c r="V11" s="81"/>
@@ -7951,7 +8085,11 @@
       <c r="X11" s="83"/>
       <c r="Y11" s="81"/>
       <c r="Z11" s="83"/>
-      <c r="AA11" s="83"/>
+      <c r="AA11" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB11" s="81"/>
       <c r="AC11" s="81"/>
       <c r="AD11" s="81"/>
@@ -7967,22 +8105,86 @@
         <v/>
       </c>
       <c r="C12" s="82"/>
-      <c r="D12" s="81"/>
+      <c r="D12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-003</t>
+        </is>
+      </c>
       <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="81"/>
+      <c r="F12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-003</t>
+        </is>
+      </c>
+      <c r="G12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speed Monitoring</t>
+        </is>
+      </c>
+      <c r="I12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case [Normal]vehicle speed changes within the valid range
+Then DD Service outputs the restriction state according to the 5/3 MPH rule, and HMI can control the corresponding features based on the state output by DD
+(Both boundaries of the 5/3 MPH rule, exercised in one sequence)</t>
+        </is>
+      </c>
+      <c r="J12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 129 (8.0625 km/h)
+2. Select "Reconfigurable menu bar" and check that it does not open
+3. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 77 (4.8125 km/h)
+4. Select "Reconfigurable menu bar" again and check that it opens</t>
+        </is>
+      </c>
+      <c r="M12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The vehicle-speed signal is carried on the bus at raw 129, which is 8.0625 km/h [ASSUMPTION A-DD6]
+2. "Reconfigurable menu bar" does not open and the screen stays as it was before the attempt
+3. The vehicle-speed signal is carried on the bus at raw 77, which is 4.8125 km/h [ASSUMPTION A-DD6]
+4. "Reconfigurable menu bar" opens and its view is displayed</t>
+        </is>
+      </c>
+      <c r="N12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915105</t>
+        </is>
+      </c>
+      <c r="O12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
+      <c r="R12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S12" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T12" s="81"/>
       <c r="U12" s="81"/>
       <c r="V12" s="81"/>
@@ -7990,7 +8192,11 @@
       <c r="X12" s="83"/>
       <c r="Y12" s="81"/>
       <c r="Z12" s="83"/>
-      <c r="AA12" s="83"/>
+      <c r="AA12" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB12" s="81"/>
       <c r="AC12" s="81"/>
       <c r="AD12" s="81"/>
@@ -8006,22 +8212,87 @@
         <v/>
       </c>
       <c r="C13" s="82"/>
-      <c r="D13" s="81"/>
+      <c r="D13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-004</t>
+        </is>
+      </c>
       <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="81"/>
+      <c r="F13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-004</t>
+        </is>
+      </c>
+      <c r="G13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speed Monitoring</t>
+        </is>
+      </c>
+      <c r="I13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When DD Service can no longer obtain a valid $Speedometer$ value through CarPropertyService
+And DD Service provides speed-input timeout monitoring and fail-safe restriction capability
+Case [Exception]the speed input is unavailable
+Then DD Service sets the Lock Out State to RESTRICTED after the input timeout
+(Fail-safe: the speed message is stopped and the menu-bar view is retried)</t>
+        </is>
+      </c>
+      <c r="J13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open "Reconfigurable menu bar", then leave it
+2. Stop transmitting the message "STATUS_CCAN3" and let the signal timeout elapse
+3. Open "Reconfigurable menu bar" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. "Reconfigurable menu bar" is displayed and accepts input, and the previous screen is shown again after leaving it
+2. The message "STATUS_CCAN3" is no longer present on the bus and the signal timeout window has elapsed
+3. "Reconfigurable menu bar" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915105</t>
+        </is>
+      </c>
+      <c r="O13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
+      <c r="R13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S13" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T13" s="81"/>
       <c r="U13" s="81"/>
       <c r="V13" s="81"/>
@@ -8029,7 +8300,11 @@
       <c r="X13" s="83"/>
       <c r="Y13" s="81"/>
       <c r="Z13" s="83"/>
-      <c r="AA13" s="83"/>
+      <c r="AA13" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB13" s="81"/>
       <c r="AC13" s="81"/>
       <c r="AD13" s="81"/>
@@ -8045,22 +8320,87 @@
         <v/>
       </c>
       <c r="C14" s="82"/>
-      <c r="D14" s="81"/>
+      <c r="D14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-005</t>
+        </is>
+      </c>
       <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="81"/>
+      <c r="F14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-005</t>
+        </is>
+      </c>
+      <c r="G14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speed Monitoring</t>
+        </is>
+      </c>
+      <c r="I14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When DD Service receives a valid $Speedometer$ value through CarPropertyService
+And DD Service provides speed monitoring, restriction-state judgment, and state notification capabilities
+Case [Normal]vehicle speed decreases from above 3 MPH to 3 MPH or below
+Then DD Service sets the Lock Out State to NOT_RESTRICTED
+(Unlock at the 3 MPH boundary, approached from above)</t>
+        </is>
+      </c>
+      <c r="J14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 129 (8.0625 km/h)
+2. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 77 (4.8125 km/h)
+3. Select "Edit phone book (speller input)" and check that it opens</t>
+        </is>
+      </c>
+      <c r="M14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The vehicle-speed signal is carried on the bus at raw 129, which is 8.0625 km/h, above the 3 MPH threshold [ASSUMPTION A-DD6]
+2. The vehicle-speed signal is carried on the bus at raw 77, which is 4.8125 km/h [ASSUMPTION A-DD6]
+3. "Edit phone book (speller input)" opens and its view is displayed</t>
+        </is>
+      </c>
+      <c r="N14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915106</t>
+        </is>
+      </c>
+      <c r="O14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q14" s="81"/>
-      <c r="R14" s="81"/>
-      <c r="S14" s="81"/>
+      <c r="R14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S14" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T14" s="81"/>
       <c r="U14" s="81"/>
       <c r="V14" s="81"/>
@@ -8068,7 +8408,11 @@
       <c r="X14" s="83"/>
       <c r="Y14" s="81"/>
       <c r="Z14" s="83"/>
-      <c r="AA14" s="83"/>
+      <c r="AA14" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB14" s="81"/>
       <c r="AC14" s="81"/>
       <c r="AD14" s="81"/>
@@ -8084,22 +8428,87 @@
         <v/>
       </c>
       <c r="C15" s="82"/>
-      <c r="D15" s="81"/>
+      <c r="D15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-006</t>
+        </is>
+      </c>
       <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="81"/>
+      <c r="F15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-006</t>
+        </is>
+      </c>
+      <c r="G15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speed Monitoring</t>
+        </is>
+      </c>
+      <c r="I15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When DD Service can no longer obtain a valid $Speedometer$ value through CarPropertyService
+And DD Service provides speed-input timeout monitoring and fail-safe restriction capability
+Case [Exception]the speed input is unavailable
+Then DD Service sets the Lock Out State to RESTRICTED after the input timeout
+(Fail-safe: the speed message is stopped and the phone book is retried)</t>
+        </is>
+      </c>
+      <c r="J15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open "Edit phone book (speller input)", then leave it
+2. Stop transmitting the message "STATUS_CCAN3" and let the signal timeout elapse
+3. Open "Edit phone book (speller input)" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. "Edit phone book (speller input)" is displayed and accepts input, and the previous screen is shown again after leaving it
+2. The message "STATUS_CCAN3" is no longer present on the bus and the signal timeout window has elapsed
+3. "Edit phone book (speller input)" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915106</t>
+        </is>
+      </c>
+      <c r="O15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
+      <c r="R15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T15" s="81"/>
       <c r="U15" s="81"/>
       <c r="V15" s="81"/>
@@ -8107,7 +8516,11 @@
       <c r="X15" s="83"/>
       <c r="Y15" s="81"/>
       <c r="Z15" s="83"/>
-      <c r="AA15" s="83"/>
+      <c r="AA15" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB15" s="81"/>
       <c r="AC15" s="81"/>
       <c r="AD15" s="81"/>
@@ -8123,22 +8536,87 @@
         <v/>
       </c>
       <c r="C16" s="82"/>
-      <c r="D16" s="81"/>
+      <c r="D16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-007</t>
+        </is>
+      </c>
       <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
+      <c r="F16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-007</t>
+        </is>
+      </c>
+      <c r="G16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speed Monitoring</t>
+        </is>
+      </c>
+      <c r="I16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When DD Service receives a valid $Speedometer$ value through CarPropertyService
+And DD Service provides speed monitoring, restriction-state judgment, and state notification capabilities
+Case [Normal]vehicle speed increases from below 5 MPH to 5 MPH or above
+Then DD Service sets the Lock Out State to RESTRICTED
+(Lock at the 5 MPH boundary, approached from below)</t>
+        </is>
+      </c>
+      <c r="J16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 77 (4.8125 km/h)
+2. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 129 (8.0625 km/h)
+3. Select "DND Customize auto reply message" and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The vehicle-speed signal is carried on the bus at raw 77, which is 4.8125 km/h, below the 5 MPH threshold [ASSUMPTION A-DD6]
+2. The vehicle-speed signal is carried on the bus at raw 129, which is 8.0625 km/h [ASSUMPTION A-DD6]
+3. "DND Customize auto reply message" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915107</t>
+        </is>
+      </c>
+      <c r="O16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
       <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
+      <c r="R16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T16" s="81"/>
       <c r="U16" s="81"/>
       <c r="V16" s="81"/>
@@ -8146,7 +8624,11 @@
       <c r="X16" s="83"/>
       <c r="Y16" s="81"/>
       <c r="Z16" s="83"/>
-      <c r="AA16" s="83"/>
+      <c r="AA16" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB16" s="81"/>
       <c r="AC16" s="81"/>
       <c r="AD16" s="81"/>
@@ -8162,22 +8644,87 @@
         <v/>
       </c>
       <c r="C17" s="82"/>
-      <c r="D17" s="81"/>
+      <c r="D17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-008</t>
+        </is>
+      </c>
       <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
+      <c r="F17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-008</t>
+        </is>
+      </c>
+      <c r="G17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speed Monitoring</t>
+        </is>
+      </c>
+      <c r="I17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When DD Service can no longer obtain a valid $Speedometer$ value through CarPropertyService
+And DD Service provides speed-input timeout monitoring and fail-safe restriction capability
+Case [Exception]the speed input is unavailable
+Then DD Service sets the Lock Out State to RESTRICTED after the input timeout
+(Fail-safe: the speed message is stopped and the auto reply editor is retried)</t>
+        </is>
+      </c>
+      <c r="J17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open "DND Customize auto reply message", then leave it
+2. Stop transmitting the message "STATUS_CCAN3" and let the signal timeout elapse
+3. Open "DND Customize auto reply message" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. "DND Customize auto reply message" is displayed and accepts input, and the previous screen is shown again after leaving it
+2. The message "STATUS_CCAN3" is no longer present on the bus and the signal timeout window has elapsed
+3. "DND Customize auto reply message" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915107</t>
+        </is>
+      </c>
+      <c r="O17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
+      <c r="R17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T17" s="81"/>
       <c r="U17" s="81"/>
       <c r="V17" s="81"/>
@@ -8185,7 +8732,11 @@
       <c r="X17" s="83"/>
       <c r="Y17" s="81"/>
       <c r="Z17" s="83"/>
-      <c r="AA17" s="83"/>
+      <c r="AA17" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB17" s="81"/>
       <c r="AC17" s="81"/>
       <c r="AD17" s="81"/>
@@ -8201,22 +8752,84 @@
         <v/>
       </c>
       <c r="C18" s="82"/>
-      <c r="D18" s="81"/>
+      <c r="D18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-009</t>
+        </is>
+      </c>
       <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
+      <c r="F18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-009</t>
+        </is>
+      </c>
+      <c r="G18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Enforcement</t>
+        </is>
+      </c>
+      <c r="I18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case [Normal]the user attempts to access a restricted feature in the lockout table
+Then DD Service outputs RESTRICTED and HMI prevents access to the feature
+(Access attempt on "Pairing (1st time)" with the speed signal held at the lock threshold)</t>
+        </is>
+      </c>
+      <c r="J18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 129 (8.0625 km/h)
+2. Open the Phone screen and select "Pairing (1st time)"
+3. Read the Phone screen and check that the pairing flow has not started</t>
+        </is>
+      </c>
+      <c r="M18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The vehicle-speed signal is carried on the bus at raw 129, which is 8.0625 km/h [ASSUMPTION A-DD6]
+2. The Phone screen is displayed and the "Pairing (1st time)" entry is selected
+3. The pairing flow does not start and the Phone screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915108</t>
+        </is>
+      </c>
+      <c r="O18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
       <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
-      <c r="S18" s="81"/>
+      <c r="R18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T18" s="81"/>
       <c r="U18" s="81"/>
       <c r="V18" s="81"/>
@@ -8224,7 +8837,11 @@
       <c r="X18" s="83"/>
       <c r="Y18" s="81"/>
       <c r="Z18" s="83"/>
-      <c r="AA18" s="83"/>
+      <c r="AA18" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB18" s="81"/>
       <c r="AC18" s="81"/>
       <c r="AD18" s="81"/>
@@ -8240,22 +8857,87 @@
         <v/>
       </c>
       <c r="C19" s="82"/>
-      <c r="D19" s="81"/>
+      <c r="D19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-010</t>
+        </is>
+      </c>
       <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="81"/>
+      <c r="F19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-010</t>
+        </is>
+      </c>
+      <c r="G19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Enforcement</t>
+        </is>
+      </c>
+      <c r="I19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When the signal simulation tool stops transmitting a vehicle message required for DD judgment
+And DD Service provides signal-timeout fail-safe behavior, and HMI applies lockout for RESTRICTED
+Case [Exception]a required vehicle signal is unavailable
+Then DD Service outputs RESTRICTED and HMI keeps the corresponding feature locked
+(Fail-safe: the speed message is stopped and "Pairing (1st time)" is retried after the timeout)</t>
+        </is>
+      </c>
+      <c r="J19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Start "Pairing (1st time)" from the Phone screen, then leave it
+2. Stop transmitting the message "STATUS_CCAN3" and let the signal timeout elapse
+3. Select "Pairing (1st time)" again and check that the pairing flow does not start</t>
+        </is>
+      </c>
+      <c r="M19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The "Pairing (1st time)" pairing screen is shown, and the Phone screen is displayed again after leaving it
+2. The message "STATUS_CCAN3" is no longer present on the bus and the signal timeout window has elapsed
+3. The "Pairing (1st time)" pairing flow does not start and the Phone screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915108</t>
+        </is>
+      </c>
+      <c r="O19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q19" s="81"/>
-      <c r="R19" s="81"/>
-      <c r="S19" s="81"/>
+      <c r="R19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S19" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T19" s="81"/>
       <c r="U19" s="81"/>
       <c r="V19" s="81"/>
@@ -8263,7 +8945,11 @@
       <c r="X19" s="83"/>
       <c r="Y19" s="81"/>
       <c r="Z19" s="83"/>
-      <c r="AA19" s="83"/>
+      <c r="AA19" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB19" s="81"/>
       <c r="AC19" s="81"/>
       <c r="AD19" s="81"/>
@@ -8279,22 +8965,84 @@
         <v/>
       </c>
       <c r="C20" s="82"/>
-      <c r="D20" s="81"/>
+      <c r="D20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-011</t>
+        </is>
+      </c>
       <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="81"/>
+      <c r="F20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-011</t>
+        </is>
+      </c>
+      <c r="G20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Enforcement</t>
+        </is>
+      </c>
+      <c r="I20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case [Normal]the state becomes RESTRICTED while the user is using a restricted feature
+Then DD Service reports RESTRICTED and HMI displays the driver-distraction lockout notification
+(Lockout notification raised while "Reconfigurable menu bar" is being edited)</t>
+        </is>
+      </c>
+      <c r="J20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the menu-bar configuration view for "Reconfigurable menu bar"
+2. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 129 (8.0625 km/h)
+3. Read the screen and check that the Standard Lockout Popup is displayed</t>
+        </is>
+      </c>
+      <c r="M20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The menu-bar configuration view for "Reconfigurable menu bar" is displayed and accepts editing input
+2. The vehicle-speed signal is carried on the bus at raw 129, which is 8.0625 km/h [ASSUMPTION A-DD6]
+3. The Standard Lockout Popup is displayed, showing "Feature not available while the vehicle is in motion."</t>
+        </is>
+      </c>
+      <c r="N20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915109</t>
+        </is>
+      </c>
+      <c r="O20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
       <c r="Q20" s="81"/>
-      <c r="R20" s="81"/>
-      <c r="S20" s="81"/>
+      <c r="R20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S20" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T20" s="81"/>
       <c r="U20" s="81"/>
       <c r="V20" s="81"/>
@@ -8302,7 +9050,11 @@
       <c r="X20" s="83"/>
       <c r="Y20" s="81"/>
       <c r="Z20" s="83"/>
-      <c r="AA20" s="83"/>
+      <c r="AA20" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB20" s="81"/>
       <c r="AC20" s="81"/>
       <c r="AD20" s="81"/>
@@ -8318,22 +9070,87 @@
         <v/>
       </c>
       <c r="C21" s="82"/>
-      <c r="D21" s="81"/>
+      <c r="D21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-012</t>
+        </is>
+      </c>
       <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
+      <c r="F21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-012</t>
+        </is>
+      </c>
+      <c r="G21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Enforcement</t>
+        </is>
+      </c>
+      <c r="I21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When the signal simulation tool stops transmitting a vehicle message required for DD judgment
+And DD Service provides signal-timeout fail-safe behavior, and HMI applies lockout for RESTRICTED
+Case [Exception]a required vehicle signal is unavailable
+Then DD Service outputs RESTRICTED and HMI keeps the corresponding feature locked
+(Fail-safe: the speed message is stopped and "Reconfigurable menu bar" is retried after the timeout)</t>
+        </is>
+      </c>
+      <c r="J21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the "Reconfigurable menu bar" configuration view, then leave it
+2. Stop transmitting the message "STATUS_CCAN3" and let the signal timeout elapse
+3. Open the menu-bar configuration view again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The menu-bar configuration view for "Reconfigurable menu bar" is displayed and accepts editing input, and the previous screen is shown again after leaving it
+2. The message "STATUS_CCAN3" is no longer present on the bus and the signal timeout window has elapsed
+3. The menu-bar configuration view does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915109</t>
+        </is>
+      </c>
+      <c r="O21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q21" s="81"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="81"/>
+      <c r="R21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S21" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T21" s="81"/>
       <c r="U21" s="81"/>
       <c r="V21" s="81"/>
@@ -8341,7 +9158,11 @@
       <c r="X21" s="83"/>
       <c r="Y21" s="81"/>
       <c r="Z21" s="83"/>
-      <c r="AA21" s="83"/>
+      <c r="AA21" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB21" s="81"/>
       <c r="AC21" s="81"/>
       <c r="AD21" s="81"/>
@@ -8357,22 +9178,82 @@
         <v/>
       </c>
       <c r="C22" s="82"/>
-      <c r="D22" s="81"/>
+      <c r="D22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-013</t>
+        </is>
+      </c>
       <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="81"/>
+      <c r="F22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-013</t>
+        </is>
+      </c>
+      <c r="G22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Tables</t>
+        </is>
+      </c>
+      <c r="I22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case [Normal]HMI has selected the applicable lockout table and judgment Type for the All architecture
+Then DD Service outputs RESTRICTED and HMI locks features marked L/O in the table
+(Lockout of a table entry sampled from the Player row)</t>
+        </is>
+      </c>
+      <c r="J22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 129 (8.0625 km/h)
+2. Select "Player Song, artist, title, etc. (speller search)" and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The vehicle-speed signal is carried on the bus at raw 129, which is 8.0625 km/h [ASSUMPTION A-DD6]
+2. "Player Song, artist, title, etc. (speller search)" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915112</t>
+        </is>
+      </c>
+      <c r="O22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
       <c r="Q22" s="81"/>
-      <c r="R22" s="81"/>
-      <c r="S22" s="81"/>
+      <c r="R22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S22" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T22" s="81"/>
       <c r="U22" s="81"/>
       <c r="V22" s="81"/>
@@ -8380,7 +9261,11 @@
       <c r="X22" s="83"/>
       <c r="Y22" s="81"/>
       <c r="Z22" s="83"/>
-      <c r="AA22" s="83"/>
+      <c r="AA22" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB22" s="81"/>
       <c r="AC22" s="81"/>
       <c r="AD22" s="81"/>
@@ -8396,22 +9281,87 @@
         <v/>
       </c>
       <c r="C23" s="82"/>
-      <c r="D23" s="81"/>
+      <c r="D23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-014</t>
+        </is>
+      </c>
       <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="81"/>
-      <c r="P23" s="81"/>
+      <c r="F23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-014</t>
+        </is>
+      </c>
+      <c r="G23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Tables</t>
+        </is>
+      </c>
+      <c r="I23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When the signal simulation tool stops transmitting a vehicle message required for DD judgment
+And DD Service provides signal-timeout fail-safe behavior, and HMI applies lockout for RESTRICTED
+Case [Exception]a required vehicle signal is unavailable
+Then DD Service outputs RESTRICTED and HMI keeps the corresponding feature locked
+(Fail-safe: the speed message is stopped and the player search is retried)</t>
+        </is>
+      </c>
+      <c r="J23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open "Player Song, artist, title, etc. (speller search)", then leave it
+2. Stop transmitting the message "STATUS_CCAN3" and let the signal timeout elapse
+3. Open "Player Song, artist, title, etc. (speller search)" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. "Player Song, artist, title, etc. (speller search)" is displayed and accepts input, and the previous screen is shown again after leaving it
+2. The message "STATUS_CCAN3" is no longer present on the bus and the signal timeout window has elapsed
+3. "Player Song, artist, title, etc. (speller search)" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915112</t>
+        </is>
+      </c>
+      <c r="O23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q23" s="81"/>
-      <c r="R23" s="81"/>
-      <c r="S23" s="81"/>
+      <c r="R23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S23" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T23" s="81"/>
       <c r="U23" s="81"/>
       <c r="V23" s="81"/>
@@ -8419,7 +9369,11 @@
       <c r="X23" s="83"/>
       <c r="Y23" s="81"/>
       <c r="Z23" s="83"/>
-      <c r="AA23" s="83"/>
+      <c r="AA23" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB23" s="81"/>
       <c r="AC23" s="81"/>
       <c r="AD23" s="81"/>
@@ -8435,22 +9389,84 @@
         <v/>
       </c>
       <c r="C24" s="82"/>
-      <c r="D24" s="81"/>
+      <c r="D24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-015</t>
+        </is>
+      </c>
       <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="81"/>
-      <c r="N24" s="81"/>
-      <c r="O24" s="81"/>
-      <c r="P24" s="81"/>
+      <c r="F24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-015</t>
+        </is>
+      </c>
+      <c r="G24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Tables</t>
+        </is>
+      </c>
+      <c r="I24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When the signal simulation tool sends vehicle signals that change the Lock Out State to RESTRICTED
+And DD Service provides restriction-state judgment and notification, and HMI provides feature lockout
+Case [Normal]DD Service outputs RESTRICTED and HMI locks features marked L/O in the table
+(Lockout of a table entry sampled from the Phone row)</t>
+        </is>
+      </c>
+      <c r="J24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $STATUS_CCAN3.VehicleSpeedVSOSig$ = 129 (8.0625 km/h)
+2. Select "Pairing (1st time)" and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The vehicle-speed signal is carried on the bus at raw 129, which is 8.0625 km/h [ASSUMPTION A-DD6]
+2. "Pairing (1st time)" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915115</t>
+        </is>
+      </c>
+      <c r="O24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
       <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="81"/>
+      <c r="R24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
+        </is>
+      </c>
+      <c r="S24" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T24" s="81"/>
       <c r="U24" s="81"/>
       <c r="V24" s="81"/>
@@ -8458,7 +9474,11 @@
       <c r="X24" s="83"/>
       <c r="Y24" s="81"/>
       <c r="Z24" s="83"/>
-      <c r="AA24" s="83"/>
+      <c r="AA24" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB24" s="81"/>
       <c r="AC24" s="81"/>
       <c r="AD24" s="81"/>
@@ -8474,22 +9494,87 @@
         <v/>
       </c>
       <c r="C25" s="82"/>
-      <c r="D25" s="81"/>
+      <c r="D25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-016</t>
+        </is>
+      </c>
       <c r="E25" s="81"/>
-      <c r="F25" s="81"/>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="81"/>
-      <c r="L25" s="81"/>
-      <c r="M25" s="81"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="81"/>
-      <c r="P25" s="81"/>
+      <c r="F25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-016</t>
+        </is>
+      </c>
+      <c r="G25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lockout Tables</t>
+        </is>
+      </c>
+      <c r="I25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When the signal simulation tool stops transmitting a vehicle message required for DD judgment
+And DD Service provides signal-timeout fail-safe behavior, and HMI applies lockout for RESTRICTED
+Case [Exception]a required vehicle signal is unavailable
+Then DD Service outputs RESTRICTED and HMI keeps the corresponding feature locked
+(Fail-safe: the speed message is stopped and pairing is retried)</t>
+        </is>
+      </c>
+      <c r="J25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)</t>
+        </is>
+      </c>
+      <c r="K25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open "Pairing (1st time)", then leave it
+2. Stop transmitting the message "STATUS_CCAN3" and let the signal timeout elapse
+3. Open "Pairing (1st time)" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. "Pairing (1st time)" is displayed and accepts input, and the previous screen is shown again after leaving it
+2. The message "STATUS_CCAN3" is no longer present on the bus and the signal timeout window has elapsed
+3. "Pairing (1st time)" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915115</t>
+        </is>
+      </c>
+      <c r="O25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q25" s="81"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="81"/>
+      <c r="R25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S25" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T25" s="81"/>
       <c r="U25" s="81"/>
       <c r="V25" s="81"/>
@@ -8497,7 +9582,11 @@
       <c r="X25" s="83"/>
       <c r="Y25" s="81"/>
       <c r="Z25" s="83"/>
-      <c r="AA25" s="83"/>
+      <c r="AA25" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB25" s="81"/>
       <c r="AC25" s="81"/>
       <c r="AD25" s="81"/>
@@ -8513,22 +9602,88 @@
         <v/>
       </c>
       <c r="C26" s="82"/>
-      <c r="D26" s="81"/>
+      <c r="D26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-017</t>
+        </is>
+      </c>
       <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="81"/>
-      <c r="L26" s="81"/>
-      <c r="M26" s="81"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="81"/>
-      <c r="P26" s="81"/>
+      <c r="F26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-017</t>
+        </is>
+      </c>
+      <c r="G26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When Country_Code is Hong Kong
+And DD Service obtains valid VC_Trans_Equipped and PresentGear inputs
+Case [Normal]VC_Trans_Equipped is Automatic and PresentGear is P
+Then DD Service sets the Lock Out State to NOT_RESTRICTED and notifies the subscribed Listener
+(Automatic transmission with the gear selector in Park)</t>
+        </is>
+      </c>
+      <c r="J26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 4 (ATX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ = 12 (Park)
+2. Open "Pairing (1st time)" and check that it opens</t>
+        </is>
+      </c>
+      <c r="M26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ is carried on the bus at 12 (Park)
+2. "Pairing (1st time)" opens and its view is displayed</t>
+        </is>
+      </c>
+      <c r="N26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915121</t>
+        </is>
+      </c>
+      <c r="O26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q26" s="81"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="81"/>
+      <c r="R26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決策表 (Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="S26" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T26" s="81"/>
       <c r="U26" s="81"/>
       <c r="V26" s="81"/>
@@ -8536,7 +9691,11 @@
       <c r="X26" s="83"/>
       <c r="Y26" s="81"/>
       <c r="Z26" s="83"/>
-      <c r="AA26" s="83"/>
+      <c r="AA26" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB26" s="81"/>
       <c r="AC26" s="81"/>
       <c r="AD26" s="81"/>
@@ -8552,22 +9711,92 @@
         <v/>
       </c>
       <c r="C27" s="82"/>
-      <c r="D27" s="81"/>
+      <c r="D27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-018</t>
+        </is>
+      </c>
       <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="81"/>
-      <c r="N27" s="81"/>
-      <c r="O27" s="81"/>
-      <c r="P27" s="81"/>
+      <c r="F27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-018</t>
+        </is>
+      </c>
+      <c r="G27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When Country_Code is Hong Kong
+And DD Service cannot obtain valid VC_Trans_Equipped or PresentGear input
+Case [Exception]the transmission configuration or dynamic gear input required for judgment is unavailable
+Then DD Service sets the Lock Out State to RESTRICTED and notifies the subscribed Listener
+(Fail-safe: the gear message is stopped and pairing is retried)</t>
+        </is>
+      </c>
+      <c r="J27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 4 (ATX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ = 12 (Park)
+2. Open "Pairing (1st time)", then leave it
+3. Stop transmitting the message "PT_SYSTEM_FD_1" and let the input timeout elapse
+4. Open "Pairing (1st time)" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ is carried on the bus at 12 (Park)
+2. "Pairing (1st time)" opens and its view is displayed, and the previous screen is shown again after leaving it
+3. The message "PT_SYSTEM_FD_1" is no longer present on the bus and the input timeout window has elapsed
+4. "Pairing (1st time)" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915121</t>
+        </is>
+      </c>
+      <c r="O27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q27" s="81"/>
-      <c r="R27" s="81"/>
-      <c r="S27" s="81"/>
+      <c r="R27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S27" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T27" s="81"/>
       <c r="U27" s="81"/>
       <c r="V27" s="81"/>
@@ -8575,7 +9804,11 @@
       <c r="X27" s="83"/>
       <c r="Y27" s="81"/>
       <c r="Z27" s="83"/>
-      <c r="AA27" s="83"/>
+      <c r="AA27" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB27" s="81"/>
       <c r="AC27" s="81"/>
       <c r="AD27" s="81"/>
@@ -8591,22 +9824,88 @@
         <v/>
       </c>
       <c r="C28" s="82"/>
-      <c r="D28" s="81"/>
+      <c r="D28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-019</t>
+        </is>
+      </c>
       <c r="E28" s="81"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="81"/>
-      <c r="L28" s="81"/>
-      <c r="M28" s="81"/>
-      <c r="N28" s="81"/>
-      <c r="O28" s="81"/>
-      <c r="P28" s="81"/>
+      <c r="F28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-019</t>
+        </is>
+      </c>
+      <c r="G28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When Country_Code is Hong Kong
+And DD Service obtains valid VC_Trans_Equipped and PresentGear inputs
+Case [Normal]VC_Trans_Equipped is Automatic and PresentGear is not P
+Then DD Service sets the Lock Out State to RESTRICTED and notifies the subscribed Listener
+(Automatic transmission with the gear selector away from Park)</t>
+        </is>
+      </c>
+      <c r="J28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 4 (ATX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ = 15 (Drive)
+2. Open "Reconfigurable menu bar" and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ is carried on the bus at 15 (Drive)
+2. "Reconfigurable menu bar" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915122</t>
+        </is>
+      </c>
+      <c r="O28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
       <c r="Q28" s="81"/>
-      <c r="R28" s="81"/>
-      <c r="S28" s="81"/>
+      <c r="R28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決策表 (Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="S28" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T28" s="81"/>
       <c r="U28" s="81"/>
       <c r="V28" s="81"/>
@@ -8614,7 +9913,11 @@
       <c r="X28" s="83"/>
       <c r="Y28" s="81"/>
       <c r="Z28" s="83"/>
-      <c r="AA28" s="83"/>
+      <c r="AA28" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB28" s="81"/>
       <c r="AC28" s="81"/>
       <c r="AD28" s="81"/>
@@ -8630,22 +9933,92 @@
         <v/>
       </c>
       <c r="C29" s="82"/>
-      <c r="D29" s="81"/>
+      <c r="D29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-020</t>
+        </is>
+      </c>
       <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-      <c r="M29" s="81"/>
-      <c r="N29" s="81"/>
-      <c r="O29" s="81"/>
-      <c r="P29" s="81"/>
+      <c r="F29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-020</t>
+        </is>
+      </c>
+      <c r="G29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When Country_Code is Hong Kong
+And DD Service cannot obtain valid VC_Trans_Equipped or PresentGear input
+Case [Exception]the transmission configuration or dynamic gear input required for judgment is unavailable
+Then DD Service sets the Lock Out State to RESTRICTED and notifies the subscribed Listener
+(Fail-safe: the gear message is stopped and the menu-bar view is retried)</t>
+        </is>
+      </c>
+      <c r="J29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 4 (ATX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ = 12 (Park)
+2. Open "Reconfigurable menu bar", then leave it
+3. Stop transmitting the message "PT_SYSTEM_FD_1" and let the input timeout elapse
+4. Open "Reconfigurable menu bar" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $PT_SYSTEM_FD_1.GearEngagedForDisplay_PT$ is carried on the bus at 12 (Park)
+2. "Reconfigurable menu bar" opens and its view is displayed, and the previous screen is shown again after leaving it
+3. The message "PT_SYSTEM_FD_1" is no longer present on the bus and the input timeout window has elapsed
+4. "Reconfigurable menu bar" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915122</t>
+        </is>
+      </c>
+      <c r="O29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q29" s="81"/>
-      <c r="R29" s="81"/>
-      <c r="S29" s="81"/>
+      <c r="R29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S29" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T29" s="81"/>
       <c r="U29" s="81"/>
       <c r="V29" s="81"/>
@@ -8653,7 +10026,11 @@
       <c r="X29" s="83"/>
       <c r="Y29" s="81"/>
       <c r="Z29" s="83"/>
-      <c r="AA29" s="83"/>
+      <c r="AA29" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB29" s="81"/>
       <c r="AC29" s="81"/>
       <c r="AD29" s="81"/>
@@ -8669,22 +10046,88 @@
         <v/>
       </c>
       <c r="C30" s="82"/>
-      <c r="D30" s="81"/>
+      <c r="D30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-021</t>
+        </is>
+      </c>
       <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
-      <c r="M30" s="81"/>
-      <c r="N30" s="81"/>
-      <c r="O30" s="81"/>
-      <c r="P30" s="81"/>
+      <c r="F30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-021</t>
+        </is>
+      </c>
+      <c r="G30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When Country_Code is Hong Kong
+And DD Service obtains valid VC_Trans_Equipped and PARK_BRK_EGD inputs
+Case [Normal]VC_Trans_Equipped is Manual and PARK_BRK_EGD is ON
+Then DD Service sets the Lock Out State to NOT_RESTRICTED and notifies the subscribed Listener
+(Manual transmission with the parking brake applied)</t>
+        </is>
+      </c>
+      <c r="J30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 1 (MTX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $BCM_FD_9.ParkBrakeSts$ = 1 (ON) [ASSUMPTION A-DD2]
+2. Open "Edit phone book (speller input)" and check that it opens</t>
+        </is>
+      </c>
+      <c r="M30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $BCM_FD_9.ParkBrakeSts$ is carried on the bus at 1 (ON) [ASSUMPTION A-DD2]
+2. "Edit phone book (speller input)" opens and its view is displayed</t>
+        </is>
+      </c>
+      <c r="N30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915123</t>
+        </is>
+      </c>
+      <c r="O30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q30" s="81"/>
-      <c r="R30" s="81"/>
-      <c r="S30" s="81"/>
+      <c r="R30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決策表 (Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="S30" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T30" s="81"/>
       <c r="U30" s="81"/>
       <c r="V30" s="81"/>
@@ -8692,7 +10135,11 @@
       <c r="X30" s="83"/>
       <c r="Y30" s="81"/>
       <c r="Z30" s="83"/>
-      <c r="AA30" s="83"/>
+      <c r="AA30" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB30" s="81"/>
       <c r="AC30" s="81"/>
       <c r="AD30" s="81"/>
@@ -8708,22 +10155,92 @@
         <v/>
       </c>
       <c r="C31" s="82"/>
-      <c r="D31" s="81"/>
+      <c r="D31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-022</t>
+        </is>
+      </c>
       <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="81"/>
-      <c r="M31" s="81"/>
-      <c r="N31" s="81"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="81"/>
+      <c r="F31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-022</t>
+        </is>
+      </c>
+      <c r="G31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When Country_Code is Hong Kong
+And DD Service cannot obtain valid VC_Trans_Equipped or PARK_BRK_EGD input
+Case [Exception]the transmission configuration or parking-brake input required for judgment is unavailable
+Then DD Service sets the Lock Out State to RESTRICTED and notifies the subscribed Listener
+(Fail-safe: the parking-brake message is stopped and the phone book is retried)</t>
+        </is>
+      </c>
+      <c r="J31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 1 (MTX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $BCM_FD_9.ParkBrakeSts$ = 1 (ON) [ASSUMPTION A-DD2]
+2. Open "Edit phone book (speller input)", then leave it
+3. Stop transmitting the message "BCM_FD_9" and let the input timeout elapse
+4. Open "Edit phone book (speller input)" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $BCM_FD_9.ParkBrakeSts$ is carried on the bus at 1 (ON) [ASSUMPTION A-DD2]
+2. "Edit phone book (speller input)" opens and its view is displayed, and the previous screen is shown again after leaving it
+3. The message "BCM_FD_9" is no longer present on the bus and the input timeout window has elapsed
+4. "Edit phone book (speller input)" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915123</t>
+        </is>
+      </c>
+      <c r="O31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q31" s="81"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="81"/>
+      <c r="R31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S31" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T31" s="81"/>
       <c r="U31" s="81"/>
       <c r="V31" s="81"/>
@@ -8731,7 +10248,11 @@
       <c r="X31" s="83"/>
       <c r="Y31" s="81"/>
       <c r="Z31" s="83"/>
-      <c r="AA31" s="83"/>
+      <c r="AA31" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB31" s="81"/>
       <c r="AC31" s="81"/>
       <c r="AD31" s="81"/>
@@ -8747,22 +10268,88 @@
         <v/>
       </c>
       <c r="C32" s="82"/>
-      <c r="D32" s="81"/>
+      <c r="D32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-023</t>
+        </is>
+      </c>
       <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="81"/>
-      <c r="M32" s="81"/>
-      <c r="N32" s="81"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="81"/>
+      <c r="F32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-023</t>
+        </is>
+      </c>
+      <c r="G32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC1:
+When Country_Code is Hong Kong
+And DD Service obtains valid VC_Trans_Equipped and PARK_BRK_EGD inputs
+Case [Normal]VC_Trans_Equipped is Manual and PARK_BRK_EGD is OFF
+Then DD Service sets the Lock Out State to RESTRICTED and notifies the subscribed Listener
+(Manual transmission with the parking brake released)</t>
+        </is>
+      </c>
+      <c r="J32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 1 (MTX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $BCM_FD_9.ParkBrakeSts$ = 0 (OFF) [ASSUMPTION A-DD2]
+2. Open "DND Customize auto reply message" and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $BCM_FD_9.ParkBrakeSts$ is carried on the bus at 0 (OFF) [ASSUMPTION A-DD2]
+2. "DND Customize auto reply message" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915124</t>
+        </is>
+      </c>
+      <c r="O32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
       <c r="Q32" s="81"/>
-      <c r="R32" s="81"/>
-      <c r="S32" s="81"/>
+      <c r="R32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決策表 (Decision Table Testing)</t>
+        </is>
+      </c>
+      <c r="S32" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T32" s="81"/>
       <c r="U32" s="81"/>
       <c r="V32" s="81"/>
@@ -8770,7 +10357,11 @@
       <c r="X32" s="83"/>
       <c r="Y32" s="81"/>
       <c r="Z32" s="83"/>
-      <c r="AA32" s="83"/>
+      <c r="AA32" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB32" s="81"/>
       <c r="AC32" s="81"/>
       <c r="AD32" s="81"/>
@@ -8786,22 +10377,92 @@
         <v/>
       </c>
       <c r="C33" s="82"/>
-      <c r="D33" s="81"/>
+      <c r="D33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWE1-RA-Driver_Distraction-024</t>
+        </is>
+      </c>
       <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="81"/>
-      <c r="L33" s="81"/>
-      <c r="M33" s="81"/>
-      <c r="N33" s="81"/>
-      <c r="O33" s="81"/>
-      <c r="P33" s="81"/>
+      <c r="F33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newR1L-DD-024</t>
+        </is>
+      </c>
+      <c r="G33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver Distraction</t>
+        </is>
+      </c>
+      <c r="H33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong Market</t>
+        </is>
+      </c>
+      <c r="I33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AC2:
+When Country_Code is Hong Kong
+And DD Service cannot obtain valid VC_Trans_Equipped or PARK_BRK_EGD input
+Case [Exception]the transmission configuration or parking-brake input required for judgment is unavailable
+Then DD Service sets the Lock Out State to RESTRICTED and notifies the subscribed Listener
+(Fail-safe: the parking-brake message is stopped and the auto reply editor is retried)</t>
+        </is>
+      </c>
+      <c r="J33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $STATUS_CCAN3.VehicleSpeedVSOSig$ is transmitted on the bus at 0 (0.0000 km/h)
+2. PROXI Country_Code = 91
+3. PROXI Gear_Box_Type = 1 (MTX) [ASSUMPTION A-DD8] [ASSUMPTION A-DD9]</t>
+        </is>
+      </c>
+      <c r="K33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
+      <c r="L33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Send the signal $BCM_FD_9.ParkBrakeSts$ = 1 (ON) [ASSUMPTION A-DD2]
+2. Open "DND Customize auto reply message", then leave it
+3. Stop transmitting the message "BCM_FD_9" and let the input timeout elapse
+4. Open "DND Customize auto reply message" again and check that it does not open</t>
+        </is>
+      </c>
+      <c r="M33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The signal $BCM_FD_9.ParkBrakeSts$ is carried on the bus at 1 (ON) [ASSUMPTION A-DD2]
+2. "DND Customize auto reply message" opens and its view is displayed, and the previous screen is shown again after leaving it
+3. The message "BCM_FD_9" is no longer present on the bus and the input timeout window has elapsed
+4. "DND Customize auto reply message" does not open and the screen stays as it was before the attempt</t>
+        </is>
+      </c>
+      <c r="N33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CFTS022-4915120
+CFTS022-4915124</t>
+        </is>
+      </c>
+      <c r="O33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW</t>
+        </is>
+      </c>
+      <c r="P33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
       <c r="Q33" s="81"/>
-      <c r="R33" s="81"/>
-      <c r="S33" s="81"/>
+      <c r="R33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基礎故障注入 (Fault Injection Lite)</t>
+        </is>
+      </c>
+      <c r="S33" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NA</t>
+        </is>
+      </c>
       <c r="T33" s="81"/>
       <c r="U33" s="81"/>
       <c r="V33" s="81"/>
@@ -8809,7 +10470,11 @@
       <c r="X33" s="83"/>
       <c r="Y33" s="81"/>
       <c r="Z33" s="83"/>
-      <c r="AA33" s="83"/>
+      <c r="AA33" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeiPYHsu</t>
+        </is>
+      </c>
       <c r="AB33" s="81"/>
       <c r="AC33" s="81"/>
       <c r="AD33" s="81"/>
